--- a/Supporting_file.xlsx
+++ b/Supporting_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\udith\Desktop\Backup\D\Uditha Design Works\Design\2026\01.Templates\SLD Genarator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DE2789-73E2-49F4-9BFB-377D78722E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781BAB71-3711-4A5F-A25D-28408FBED1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="112">
   <si>
     <t>Inverters</t>
   </si>
@@ -315,6 +315,63 @@
   </si>
   <si>
     <t>50mm2 Cu/ PVc Earth Cable</t>
+  </si>
+  <si>
+    <t>Sungrow</t>
+  </si>
+  <si>
+    <t>Sungrow Hybrid</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG5.0RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG6.0RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG7.0RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG8.0RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG10.0RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG12.0RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG15RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG17RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG20RT-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG36CX-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG40CX-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG50CX-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SH50CX)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SH125CX)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SH80CX)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG110CX-P2)</t>
+  </si>
+  <si>
+    <t>000.00.00 (Sungrow-SG100CX-P2)</t>
   </si>
 </sst>
 </file>
@@ -343,7 +400,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,6 +467,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -423,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
@@ -456,6 +519,11 @@
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection hidden="1"/>
@@ -464,11 +532,14 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C5:K83"/>
+  <dimension ref="C5:K101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="38.5703125" customWidth="1"/>
@@ -798,22 +869,22 @@
       <c r="D5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -830,7 +901,7 @@
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="9"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
@@ -845,7 +916,7 @@
       </c>
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C8" s="9"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
@@ -860,7 +931,7 @@
       </c>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="9"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="3" t="s">
         <v>5</v>
       </c>
@@ -875,14 +946,14 @@
       </c>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C10" s="9"/>
+      <c r="C10" s="11"/>
       <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E10">
         <v>31.9</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="9" t="s">
         <v>77</v>
       </c>
       <c r="G10" t="s">
@@ -890,14 +961,14 @@
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" s="9"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G11" t="s">
@@ -905,14 +976,14 @@
       </c>
     </row>
     <row r="12" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C12" s="9"/>
+      <c r="C12" s="11"/>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E12">
         <v>16</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G12" t="s">
@@ -920,7 +991,7 @@
       </c>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -937,7 +1008,7 @@
       </c>
     </row>
     <row r="14" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C14" s="9"/>
+      <c r="C14" s="11"/>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
@@ -952,7 +1023,7 @@
       </c>
     </row>
     <row r="15" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C15" s="9"/>
+      <c r="C15" s="11"/>
       <c r="D15" s="4" t="s">
         <v>12</v>
       </c>
@@ -967,7 +1038,7 @@
       </c>
     </row>
     <row r="16" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C16" s="9"/>
+      <c r="C16" s="11"/>
       <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
@@ -982,7 +1053,7 @@
       </c>
     </row>
     <row r="17" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C17" s="9"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="4" t="s">
         <v>14</v>
       </c>
@@ -997,7 +1068,7 @@
       </c>
     </row>
     <row r="18" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C18" s="9"/>
+      <c r="C18" s="11"/>
       <c r="D18" s="4" t="s">
         <v>15</v>
       </c>
@@ -1012,7 +1083,7 @@
       </c>
     </row>
     <row r="19" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C19" s="9"/>
+      <c r="C19" s="11"/>
       <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
@@ -1027,7 +1098,7 @@
       </c>
     </row>
     <row r="20" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C20" s="9"/>
+      <c r="C20" s="11"/>
       <c r="D20" s="4" t="s">
         <v>17</v>
       </c>
@@ -1042,7 +1113,7 @@
       </c>
     </row>
     <row r="21" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C21" s="9"/>
+      <c r="C21" s="11"/>
       <c r="D21" s="4" t="s">
         <v>18</v>
       </c>
@@ -1057,7 +1128,7 @@
       </c>
     </row>
     <row r="22" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C22" s="9"/>
+      <c r="C22" s="11"/>
       <c r="D22" s="4" t="s">
         <v>19</v>
       </c>
@@ -1072,7 +1143,7 @@
       </c>
     </row>
     <row r="23" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C23" s="9"/>
+      <c r="C23" s="11"/>
       <c r="D23" s="4" t="s">
         <v>20</v>
       </c>
@@ -1087,7 +1158,7 @@
       </c>
     </row>
     <row r="24" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C24" s="9"/>
+      <c r="C24" s="11"/>
       <c r="D24" s="4" t="s">
         <v>21</v>
       </c>
@@ -1102,14 +1173,14 @@
       </c>
     </row>
     <row r="25" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="9"/>
+      <c r="C25" s="11"/>
       <c r="D25" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E25">
         <v>57.4</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G25" t="s">
@@ -1117,14 +1188,14 @@
       </c>
     </row>
     <row r="26" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C26" s="9"/>
+      <c r="C26" s="11"/>
       <c r="D26" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E26">
         <v>52.6</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G26" t="s">
@@ -1132,14 +1203,14 @@
       </c>
     </row>
     <row r="27" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C27" s="9"/>
+      <c r="C27" s="11"/>
       <c r="D27" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E27">
         <v>47.8</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G27" t="s">
@@ -1147,14 +1218,14 @@
       </c>
     </row>
     <row r="28" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="9"/>
+      <c r="C28" s="11"/>
       <c r="D28" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E28">
         <v>43.3</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G28" t="s">
@@ -1162,14 +1233,14 @@
       </c>
     </row>
     <row r="29" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="9"/>
+      <c r="C29" s="11"/>
       <c r="D29" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E29">
         <v>39</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G29" t="s">
@@ -1177,14 +1248,14 @@
       </c>
     </row>
     <row r="30" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="9"/>
+      <c r="C30" s="11"/>
       <c r="D30" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E30">
         <v>31.9</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="9" t="s">
         <v>77</v>
       </c>
       <c r="G30" t="s">
@@ -1192,14 +1263,14 @@
       </c>
     </row>
     <row r="31" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C31" s="9"/>
+      <c r="C31" s="11"/>
       <c r="D31" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E31">
         <v>28.4</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G31" t="s">
@@ -1207,14 +1278,14 @@
       </c>
     </row>
     <row r="32" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C32" s="9"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E32">
         <v>25</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G32" t="s">
@@ -1222,14 +1293,14 @@
       </c>
     </row>
     <row r="33" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C33" s="9"/>
+      <c r="C33" s="11"/>
       <c r="D33" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G33" t="s">
@@ -1237,14 +1308,14 @@
       </c>
     </row>
     <row r="34" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C34" s="9"/>
+      <c r="C34" s="11"/>
       <c r="D34" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E34">
         <v>16.5</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G34" t="s">
@@ -1252,7 +1323,7 @@
       </c>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="11" t="s">
         <v>32</v>
       </c>
       <c r="D35" s="5" t="s">
@@ -1269,7 +1340,7 @@
       </c>
     </row>
     <row r="36" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C36" s="9"/>
+      <c r="C36" s="11"/>
       <c r="D36" s="5" t="s">
         <v>34</v>
       </c>
@@ -1284,7 +1355,7 @@
       </c>
     </row>
     <row r="37" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C37" s="9"/>
+      <c r="C37" s="11"/>
       <c r="D37" s="5" t="s">
         <v>35</v>
       </c>
@@ -1292,14 +1363,14 @@
         <v>160.4</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="38" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C38" s="9"/>
+      <c r="C38" s="11"/>
       <c r="D38" s="5" t="s">
         <v>36</v>
       </c>
@@ -1314,7 +1385,7 @@
       </c>
     </row>
     <row r="39" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C39" s="9"/>
+      <c r="C39" s="11"/>
       <c r="D39" s="5" t="s">
         <v>37</v>
       </c>
@@ -1329,14 +1400,14 @@
       </c>
     </row>
     <row r="40" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C40" s="9"/>
+      <c r="C40" s="11"/>
       <c r="D40" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E40">
         <v>58</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G40" t="s">
@@ -1344,14 +1415,14 @@
       </c>
     </row>
     <row r="41" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C41" s="9"/>
+      <c r="C41" s="11"/>
       <c r="D41" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E41">
         <v>47.9</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G41" t="s">
@@ -1359,14 +1430,14 @@
       </c>
     </row>
     <row r="42" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C42" s="9"/>
+      <c r="C42" s="11"/>
       <c r="D42" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E42">
         <v>39.9</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G42" t="s">
@@ -1374,14 +1445,14 @@
       </c>
     </row>
     <row r="43" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C43" s="9"/>
+      <c r="C43" s="11"/>
       <c r="D43" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E43">
         <v>31.9</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="9" t="s">
         <v>77</v>
       </c>
       <c r="G43" t="s">
@@ -1389,14 +1460,14 @@
       </c>
     </row>
     <row r="44" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C44" s="9"/>
+      <c r="C44" s="11"/>
       <c r="D44" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E44">
         <v>27.1</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G44" t="s">
@@ -1404,14 +1475,14 @@
       </c>
     </row>
     <row r="45" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C45" s="9"/>
+      <c r="C45" s="11"/>
       <c r="D45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E45">
         <v>23.9</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G45" t="s">
@@ -1419,14 +1490,14 @@
       </c>
     </row>
     <row r="46" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C46" s="9"/>
+      <c r="C46" s="11"/>
       <c r="D46" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E46">
         <v>17.3</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G46" t="s">
@@ -1434,14 +1505,14 @@
       </c>
     </row>
     <row r="47" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C47" s="9"/>
+      <c r="C47" s="11"/>
       <c r="D47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E47">
         <v>15</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G47" t="s">
@@ -1449,397 +1520,632 @@
       </c>
     </row>
     <row r="48" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C48" s="1"/>
+      <c r="C48" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="D48" s="6" t="s">
         <v>46</v>
       </c>
       <c r="E48">
         <v>240.6</v>
       </c>
-    </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C49" s="1"/>
+      <c r="F48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C49" s="13"/>
       <c r="D49" s="6" t="s">
         <v>47</v>
       </c>
       <c r="E49">
         <v>189.9</v>
       </c>
-    </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C50" s="1"/>
+      <c r="F49" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C50" s="13"/>
       <c r="D50" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E50">
         <v>181.1</v>
       </c>
-    </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C51" s="1"/>
+      <c r="F50" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G50" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C51" s="13"/>
       <c r="D51" s="6" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="E51">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C52" s="1"/>
+        <v>158.80000000000001</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C52" s="13"/>
       <c r="D52" s="6" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="E52">
-        <v>63.8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C53" s="1"/>
+        <v>143.30000000000001</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C53" s="13"/>
       <c r="D53" s="6" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="E53">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C54" s="13"/>
+      <c r="D54" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54">
+        <v>10</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="13"/>
+      <c r="D55" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E55">
+        <v>11.7</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C56" s="13"/>
+      <c r="D56" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E56">
+        <v>13.3</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="13"/>
+      <c r="D57" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57">
+        <v>16.7</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="13"/>
+      <c r="D58" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E58">
+        <v>20</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="13"/>
+      <c r="D59" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E59">
+        <v>25</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="13"/>
+      <c r="D60" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E60">
+        <v>28.3</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="13"/>
+      <c r="D61" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61">
+        <v>31.9</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C62" s="13"/>
+      <c r="D62" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E62">
+        <v>60.2</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C63" s="13"/>
+      <c r="D63" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="13"/>
+      <c r="D64" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64">
+        <v>83.6</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C66" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66">
+        <v>55</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C67" s="12"/>
+      <c r="D67" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67">
+        <v>50</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C68" s="12"/>
+      <c r="D68" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68">
+        <v>41.7</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C69" s="12"/>
+      <c r="D69" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C70" s="12"/>
+      <c r="D70" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70">
+        <v>28.3</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C71" s="12"/>
+      <c r="D71" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E71">
+        <v>25</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C72" s="12"/>
+      <c r="D72" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72">
+        <v>20</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C73" s="12"/>
+      <c r="D73" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E73">
+        <v>16.5</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C74" s="12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C54" s="1"/>
-      <c r="D54" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54">
-        <v>47.9</v>
-      </c>
-    </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C55" s="1"/>
-      <c r="D55" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E55">
-        <v>39.9</v>
-      </c>
-    </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C56" s="1"/>
-      <c r="D56" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E56">
-        <v>31.9</v>
-      </c>
-    </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C57" s="1"/>
-      <c r="D57" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E57">
-        <v>27.1</v>
-      </c>
-    </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C58" s="1"/>
-      <c r="D58" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E58">
-        <v>23.9</v>
-      </c>
-    </row>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C59" s="1"/>
-      <c r="D59" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E59">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C60" s="1"/>
-      <c r="D60" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C62" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62">
-        <v>55</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C63" s="10"/>
-      <c r="D63" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E63">
-        <v>50</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C64" s="10"/>
-      <c r="D64" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E64">
-        <v>41.7</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C65" s="10"/>
-      <c r="D65" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E65">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C66" s="10"/>
-      <c r="D66" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E66">
-        <v>28.3</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C67" s="10"/>
-      <c r="D67" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E67">
-        <v>25</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C68" s="10"/>
-      <c r="D68" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E68">
-        <v>20</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C69" s="10"/>
-      <c r="D69" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E69">
-        <v>16.5</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C70" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D70" s="8" t="s">
+      <c r="D74" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E70">
+      <c r="E74">
         <v>181</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F74" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C71" s="10"/>
-      <c r="D71" s="8" t="s">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C75" s="12"/>
+      <c r="D75" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E71">
+      <c r="E75">
         <v>144</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C72" s="10"/>
-      <c r="D72" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E72">
-        <v>217</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C73" s="10"/>
-      <c r="D73" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E73">
-        <v>144</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C74" s="10"/>
-      <c r="D74" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E74">
-        <v>217</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C75" s="10"/>
-      <c r="D75" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E75">
-        <v>173</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C76" s="10"/>
+      <c r="C76" s="12"/>
       <c r="D76" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76">
+        <v>217</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C77" s="12"/>
+      <c r="D77" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77">
+        <v>144</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C78" s="12"/>
+      <c r="D78" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E78">
+        <v>217</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C79" s="12"/>
+      <c r="D79" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79">
+        <v>173</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C80" s="12"/>
+      <c r="D80" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E76">
+      <c r="E80">
         <v>144</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F80" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C77" s="10"/>
-      <c r="D77" s="8" t="s">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C81" s="12"/>
+      <c r="D81" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E77">
+      <c r="E81">
         <v>72</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F81" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C78" s="10"/>
-      <c r="D78" s="8" t="s">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C82" s="12"/>
+      <c r="D82" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E78">
+      <c r="E82">
         <v>43</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F82" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C79" s="10"/>
-      <c r="D79" s="8" t="s">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C83" s="12"/>
+      <c r="D83" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E79">
+      <c r="E83">
         <v>72</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F83" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C80" s="10"/>
-      <c r="D80" s="8" t="s">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C84" s="12"/>
+      <c r="D84" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E80">
+      <c r="E84">
         <v>57</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F84" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C81" s="10"/>
-      <c r="D81" s="8" t="s">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C85" s="12"/>
+      <c r="D85" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E81">
+      <c r="E85">
         <v>43</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F85" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C82" s="10"/>
-      <c r="D82" s="8" t="s">
+    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C86" s="12"/>
+      <c r="D86" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E82">
+      <c r="E86">
         <v>28</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F86" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C83" s="10"/>
-      <c r="D83" s="8" t="s">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C87" s="12"/>
+      <c r="D87" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E83">
+      <c r="E87">
         <v>21</v>
       </c>
-      <c r="F83" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="F87" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C88" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E88">
+        <v>108.3</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C89" s="12"/>
+      <c r="D89" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E89">
+        <v>173.2</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C90" s="12"/>
+      <c r="D90" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E90">
+        <v>270.60000000000002</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C91" s="12"/>
+      <c r="D91" s="14"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C92" s="12"/>
+      <c r="D92" s="14"/>
+      <c r="F92" s="6"/>
+    </row>
+    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C93" s="12"/>
+      <c r="D93" s="14"/>
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C94" s="12"/>
+      <c r="D94" s="14"/>
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C95" s="12"/>
+      <c r="D95" s="14"/>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C96" s="12"/>
+      <c r="D96" s="14"/>
+      <c r="F96" s="9"/>
+    </row>
+    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C97" s="12"/>
+      <c r="D97" s="14"/>
+      <c r="F97" s="6"/>
+    </row>
+    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C98" s="12"/>
+      <c r="D98" s="14"/>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C99" s="12"/>
+      <c r="D99" s="14"/>
+      <c r="F99" s="9"/>
+    </row>
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C100" s="12"/>
+      <c r="D100" s="14"/>
+      <c r="F100" s="9"/>
+    </row>
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C101" s="12"/>
+      <c r="D101" s="14"/>
+      <c r="F101" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="C88:C101"/>
     <mergeCell ref="C6:C12"/>
     <mergeCell ref="C13:C34"/>
     <mergeCell ref="C35:C47"/>
-    <mergeCell ref="C62:C69"/>
-    <mergeCell ref="C70:C83"/>
+    <mergeCell ref="C66:C73"/>
+    <mergeCell ref="C74:C87"/>
+    <mergeCell ref="C48:C64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
